--- a/artfynd/A 11-2024 artfynd.xlsx
+++ b/artfynd/A 11-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80894465</v>
+        <v>136988300</v>
       </c>
       <c r="B2" t="n">
-        <v>58114</v>
+        <v>57195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,25 +714,26 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>Svartsättravägen, Ubby-Långsjön, Fasterna/Gottröra, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>679982</v>
+        <v>679926</v>
       </c>
       <c r="R2" t="n">
-        <v>6632903</v>
+        <v>6632896</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-11-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-11-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,16 +777,139 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Samuel Wivstad</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Samuel Wivstad</t>
+          <t>Ingrid Ehnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136988300</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>80894465</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norrtälje, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>679982</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6632903</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fasterna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-11-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-11-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Samuel Wivstad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Samuel Wivstad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/80894465</t>
         </is>
@@ -804,6 +918,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11-2024 artfynd.xlsx
+++ b/artfynd/A 11-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988300</v>
       </c>
       <c r="B2" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11-2024 artfynd.xlsx
+++ b/artfynd/A 11-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988300</v>
       </c>
       <c r="B2" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11-2024 artfynd.xlsx
+++ b/artfynd/A 11-2024 artfynd.xlsx
@@ -714,11 +714,7 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">

--- a/artfynd/A 11-2024 artfynd.xlsx
+++ b/artfynd/A 11-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988300</v>
       </c>
       <c r="B2" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11-2024 artfynd.xlsx
+++ b/artfynd/A 11-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988300</v>
       </c>
       <c r="B2" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11-2024 artfynd.xlsx
+++ b/artfynd/A 11-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988300</v>
       </c>
       <c r="B2" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
